--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486991_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486991_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3689</v>
+        <v>8.643000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3428</v>
+        <v>7.3501</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0261</v>
+        <v>1.2929</v>
       </c>
       <c r="G2" t="n">
         <v>7.5549</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5699</v>
+        <v>0.7042</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4457</v>
+        <v>0.5616</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1243</v>
+        <v>0.1425</v>
       </c>
       <c r="V2" t="n">
         <v>0.5893</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5169</v>
+        <v>3.5922</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0427</v>
+        <v>3.7237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4742</v>
+        <v>-0.1316</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2862</v>
+        <v>1.0399</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6229</v>
+        <v>0.3927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6632</v>
+        <v>0.6472</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7721</v>
+        <v>2.5995</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7855</v>
+        <v>0.8633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9866</v>
+        <v>1.7361</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.486</v>
+        <v>-1.5596</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1626</v>
+        <v>-0.4706</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3234</v>
+        <v>-1.089</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1425</v>
+        <v>1.4907</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6464</v>
+        <v>0.9375</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4961</v>
+        <v>0.5532</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3491</v>
+        <v>0.2402</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8295</v>
+        <v>1.4189</v>
       </c>
       <c r="X3" t="n">
         <v>-1.1786</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1111</v>
+        <v>3.5755</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1537</v>
+        <v>3.1013</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0426</v>
+        <v>0.4742</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0399</v>
+        <v>1.2862</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3927</v>
+        <v>0.6229</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6472</v>
+        <v>0.6632</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5995</v>
+        <v>1.7721</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8633</v>
+        <v>0.7855</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7361</v>
+        <v>0.9866</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5596</v>
+        <v>-0.486</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4706</v>
+        <v>-0.1626</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.089</v>
+        <v>-0.3234</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0096</v>
+        <v>1.201</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3675</v>
+        <v>0.705</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6421</v>
+        <v>0.4961</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2402</v>
+        <v>-0.3491</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4189</v>
+        <v>0.8295</v>
       </c>
       <c r="X4" t="n">
         <v>-1.1786</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8507</v>
+        <v>2.1621</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8242</v>
+        <v>3.9874</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9734</v>
+        <v>-1.8252</v>
       </c>
       <c r="G5" t="n">
         <v>-2.0771</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7143</v>
+        <v>1.0257</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7781</v>
+        <v>0.9413</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0638</v>
+        <v>0.0844</v>
       </c>
       <c r="V5" t="n">
         <v>2.5975</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2039</v>
+        <v>2.0277</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8264</v>
+        <v>2.0356</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3775</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>1.4568</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3282</v>
+        <v>0.1521</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1045</v>
+        <v>0.3137</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2237</v>
+        <v>-0.1616</v>
       </c>
       <c r="V6" t="n">
         <v>0.8295</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4345</v>
+        <v>1.6165</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8432</v>
+        <v>1.9362</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4087</v>
+        <v>-0.3198</v>
       </c>
       <c r="G7" t="n">
         <v>1.0688</v>
@@ -1000,13 +1000,13 @@
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4273</v>
+        <v>0.6092</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6701</v>
+        <v>0.7631</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2428</v>
+        <v>-0.1539</v>
       </c>
       <c r="V7" t="n">
         <v>0.3491</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1218</v>
+        <v>0.7766</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2129</v>
+        <v>-1.5582</v>
       </c>
       <c r="F8" t="n">
         <v>2.3347</v>
@@ -1078,10 +1078,10 @@
         <v>2.6694</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3525</v>
+        <v>0.3022</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7091</v>
+        <v>-0.0544</v>
       </c>
       <c r="U8" t="n">
         <v>0.3566</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1137</v>
+        <v>-0.3426</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3588</v>
+        <v>0.6338</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4725</v>
+        <v>-0.9764</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7332</v>
@@ -1156,13 +1156,13 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3607</v>
+        <v>2.1319</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8832</v>
+        <v>1.1583</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4776</v>
+        <v>0.9736</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5612</v>
+        <v>-1.2467</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.222</v>
+        <v>-0.2336</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3391</v>
+        <v>-1.013</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4606</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7557</v>
+        <v>1.0702</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1698</v>
+        <v>1.1583</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4141</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8354</v>
+        <v>-2.7186</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0346</v>
+        <v>-1.066</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8008</v>
+        <v>-1.6526</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7756999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>2.2588</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.2625</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7905</v>
+        <v>0.1781</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0638</v>
+        <v>0.0844</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.0975</v>
+        <v>18.0857</v>
       </c>
       <c r="E12" t="n">
-        <v>18.9223</v>
+        <v>19.9103</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8246</v>
+        <v>-1.8247</v>
       </c>
       <c r="G12" t="n">
-        <v>5.709200000000002</v>
+        <v>5.7092</v>
       </c>
       <c r="H12" t="n">
         <v>4.329499999999999</v>
@@ -1369,7 +1369,7 @@
         <v>8.5991</v>
       </c>
       <c r="L12" t="n">
-        <v>9.376099999999999</v>
+        <v>9.376100000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-12.2662</v>
@@ -1381,7 +1381,7 @@
         <v>-7.9968</v>
       </c>
       <c r="P12" t="n">
-        <v>0.000100000000000211</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.4275</v>
@@ -1390,10 +1390,10 @@
         <v>16.4272</v>
       </c>
       <c r="S12" t="n">
-        <v>7.961599999999999</v>
+        <v>8.949699999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>5.674300000000001</v>
+        <v>6.662500000000001</v>
       </c>
       <c r="U12" t="n">
         <v>2.2873</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5215</v>
+        <v>3.1073</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6119</v>
+        <v>3.8211</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0904</v>
+        <v>-0.7138</v>
       </c>
       <c r="G13" t="n">
         <v>4.23</v>
@@ -1468,13 +1468,13 @@
         <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8953</v>
+        <v>-1.3095</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7169</v>
+        <v>-0.5077</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1785</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.4189</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9648</v>
+        <v>0.4557</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1124</v>
+        <v>0.4848</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1476</v>
+        <v>-0.0291</v>
       </c>
       <c r="G14" t="n">
         <v>0.1884</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3657</v>
+        <v>-0.1433</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0808</v>
+        <v>0.4532</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7151</v>
+        <v>-0.5965</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ROKER</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.3788</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4443</v>
+        <v>1.8417</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5409</v>
+        <v>-2.2205</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0177</v>
+        <v>-1.0222</v>
       </c>
       <c r="H15" t="n">
-        <v>2.725</v>
+        <v>-2.7376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7073</v>
+        <v>1.7154</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9404</v>
+        <v>1.9444</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8615</v>
+        <v>-1.4623</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0789</v>
+        <v>3.4067</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9227</v>
+        <v>-2.9666</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1365</v>
+        <v>-1.2753</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7863</v>
+        <v>-1.6913</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0459</v>
+        <v>-1.0896</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2907</v>
+        <v>-0.7906</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3366</v>
+        <v>-0.2991</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.1868</v>
+        <v>1.5277</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.9466</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.1868</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>A. ROKER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7222</v>
+        <v>-0.4698</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5279</v>
+        <v>2.4443</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2501</v>
+        <v>-2.9141</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0222</v>
+        <v>2.0177</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7376</v>
+        <v>2.725</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7154</v>
+        <v>-0.7073</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9444</v>
+        <v>2.9404</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4623</v>
+        <v>2.8615</v>
       </c>
       <c r="L16" t="n">
-        <v>3.4067</v>
+        <v>0.0789</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9666</v>
+        <v>-0.9227</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2753</v>
+        <v>-0.1365</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6913</v>
+        <v>-0.7863</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4641</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4331</v>
+        <v>-0.3273</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1044</v>
+        <v>-0.2907</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3287</v>
+        <v>-0.0366</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5277</v>
+        <v>-3.1868</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9466</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4189</v>
+        <v>-3.1868</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>E. COLL COMABELLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3988</v>
+        <v>-1.3432</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4222</v>
+        <v>0.2817</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9766</v>
+        <v>-1.6249</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6209</v>
+        <v>0.5909</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4396</v>
+        <v>0.104</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1812</v>
+        <v>0.487</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1142</v>
+        <v>1.2194</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7192</v>
+        <v>0.5485</v>
       </c>
       <c r="L17" t="n">
-        <v>0.605</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5067</v>
+        <v>-0.6284</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7204</v>
+        <v>-0.4445</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7863</v>
+        <v>-0.1839</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.6694</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2953</v>
+        <v>-0.5502</v>
       </c>
       <c r="T17" t="n">
-        <v>0.612</v>
+        <v>0.0891</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9073</v>
+        <v>-0.6392</v>
       </c>
       <c r="V17" t="n">
-        <v>3.1868</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>3.1868</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. COLL COMABELLA</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1591</v>
+        <v>-1.5452</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1367</v>
+        <v>-0.9453</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0224</v>
+        <v>-0.6</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5909</v>
+        <v>-1.6209</v>
       </c>
       <c r="H18" t="n">
-        <v>0.104</v>
+        <v>-1.4396</v>
       </c>
       <c r="I18" t="n">
-        <v>0.487</v>
+        <v>-0.1812</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2194</v>
+        <v>-0.1142</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5485</v>
+        <v>-0.7192</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6284</v>
+        <v>-1.5067</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4445</v>
+        <v>-0.7204</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1839</v>
+        <v>-0.7863</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2053</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3661</v>
+        <v>-0.4417</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3294</v>
+        <v>0.089</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0367</v>
+        <v>-0.5306</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1786</v>
+        <v>3.1868</v>
       </c>
       <c r="W18" t="n">
+        <v>3.1868</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4468</v>
+        <v>-2.459</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3315</v>
+        <v>-0.0176</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1153</v>
+        <v>-2.4414</v>
       </c>
       <c r="G19" t="n">
         <v>0.08939999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6163</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5192</v>
+        <v>-0.2054</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.097</v>
+        <v>-0.4231</v>
       </c>
       <c r="V19" t="n">
         <v>-2.9466</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1218</v>
+        <v>-3.2281</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2851</v>
+        <v>-0.0287</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4069</v>
+        <v>-3.1994</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0926</v>
@@ -2014,13 +2014,13 @@
         <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5281</v>
+        <v>-0.6344</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2517</v>
+        <v>-0.0621</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7798</v>
+        <v>-0.5723</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8394</v>
+        <v>-3.9502</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9522</v>
+        <v>-1.6384</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8872</v>
+        <v>-2.3118</v>
       </c>
       <c r="G21" t="n">
         <v>-3.7812</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9062</v>
+        <v>-1.0171</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.054</v>
+        <v>-0.7401</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.2769</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5893</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7993</v>
+        <v>-5.8917</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3144</v>
+        <v>-4.419</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4849</v>
+        <v>-1.4728</v>
       </c>
       <c r="G22" t="n">
         <v>-4.3084</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3328</v>
+        <v>-0.4252</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2171</v>
+        <v>-0.3217</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1156</v>
+        <v>-0.1035</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1314</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-17.0977</v>
+        <v>-15.703</v>
       </c>
       <c r="E23" t="n">
-        <v>1.824600000000001</v>
+        <v>1.824599999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.9223</v>
+        <v>-17.5278</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7089</v>
@@ -2248,13 +2248,13 @@
         <v>16.4274</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.9616</v>
+        <v>-6.5668</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.2872</v>
+        <v>-2.287</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.674399999999999</v>
+        <v>-4.279700000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-3.427000000000001</v>
